--- a/exports/VEDL_full_report.xlsx
+++ b/exports/VEDL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>145.8</v>
+        <v>141.7</v>
       </c>
       <c r="I2" t="n">
         <v>144.978248376975</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.2</v>
+        <v>-6.9</v>
       </c>
       <c r="L2" t="n">
-        <v>5.88</v>
+        <v>7.49</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>4.29</v>
       </c>
       <c r="O2" t="n">
         <v>0.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.74</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>147.8</v>
+        <v>152.4</v>
       </c>
       <c r="I3" t="n">
         <v>150.6962451659489</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.3</v>
+        <v>-7.55</v>
       </c>
       <c r="L3" t="n">
-        <v>6.95</v>
+        <v>8.01</v>
       </c>
       <c r="M3" t="n">
         <v>0.73</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.28</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>160.05</v>
+        <v>154.85</v>
       </c>
       <c r="I4" t="n">
         <v>159.3154749183771</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02</v>
+        <v>1.61</v>
       </c>
       <c r="L4" t="n">
         <v>3.28</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>164.05</v>
+        <v>169.55</v>
       </c>
       <c r="I5" t="n">
         <v>167.3791688894436</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.94</v>
+        <v>-9.49</v>
       </c>
       <c r="L5" t="n">
-        <v>7.1</v>
+        <v>10.2</v>
       </c>
       <c r="M5" t="n">
         <v>1.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44635.38541666666</v>
+        <v>44635.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>163.95</v>
+        <v>161.75</v>
       </c>
       <c r="I6" t="n">
         <v>162.5707905660424</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.3</v>
+        <v>-4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>4.66</v>
+        <v>5.51</v>
       </c>
       <c r="M6" t="n">
         <v>2.92</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44637.55208333334</v>
+        <v>44641.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>172.15</v>
+        <v>182.9</v>
       </c>
       <c r="I7" t="n">
         <v>176.9313871419548</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.43</v>
+        <v>-13.08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.64</v>
+        <v>14.1</v>
       </c>
       <c r="M7" t="n">
         <v>1.51</v>
       </c>
       <c r="N7" t="n">
-        <v>4.67</v>
+        <v>5.75</v>
       </c>
       <c r="O7" t="n">
         <v>-5.13</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>10.93</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>191.1</v>
+        <v>184.5</v>
       </c>
       <c r="I8" t="n">
         <v>187.5284458467262</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>4.48</v>
+        <v>0.87</v>
       </c>
       <c r="L8" t="n">
         <v>5.06</v>
       </c>
       <c r="M8" t="n">
-        <v>1.34</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
         <v>4.32</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.39</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44757.55208333334</v>
+        <v>44760.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>99.40000000000001</v>
+        <v>102.85</v>
       </c>
       <c r="I9" t="n">
         <v>101.7574827790934</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>46.12</v>
+        <v>44.25</v>
       </c>
       <c r="L9" t="n">
         <v>4.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.19</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>140.75</v>
+        <v>129.6</v>
       </c>
       <c r="I10" t="n">
         <v>129.6780380614858</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>36.85</v>
+        <v>26.01</v>
       </c>
       <c r="L10" t="n">
         <v>2.67</v>
@@ -1011,7 +1130,7 @@
         <v>7.63</v>
       </c>
       <c r="N10" t="n">
-        <v>7.06</v>
+        <v>7.99</v>
       </c>
       <c r="O10" t="n">
         <v>4.48</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.97</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>124.15</v>
+        <v>130.45</v>
       </c>
       <c r="I11" t="n">
         <v>124.2456001401057</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>4.21</v>
+        <v>-0.66</v>
       </c>
       <c r="L11" t="n">
         <v>2.82</v>
@@ -1068,7 +1199,7 @@
         <v>4.29</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>5.24</v>
       </c>
       <c r="O11" t="n">
         <v>-7.99</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.01</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>138.2</v>
+        <v>135.95</v>
       </c>
       <c r="I12" t="n">
         <v>136.2869730790225</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>76</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>5.94</v>
+        <v>4.22</v>
       </c>
       <c r="L12" t="n">
         <v>6.82</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.37</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44922.38541666666</v>
+        <v>44922.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>137.4</v>
+        <v>137.85</v>
       </c>
       <c r="I13" t="n">
         <v>137.7204766790989</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.07</v>
+        <v>-1.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
         <v>1.17</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.37</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>147.4</v>
+        <v>142.65</v>
       </c>
       <c r="I14" t="n">
         <v>143.6460747679718</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>29</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>6.93</v>
+        <v>3.48</v>
       </c>
       <c r="L14" t="n">
         <v>2.29</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>124.2</v>
+        <v>126.65</v>
       </c>
       <c r="I15" t="n">
         <v>126.2807193286728</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>101.1666666666667</v>
+        <v>102</v>
       </c>
       <c r="K15" t="n">
-        <v>12.93</v>
+        <v>11.22</v>
       </c>
       <c r="L15" t="n">
         <v>7.05</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45058.38541666666</v>
+        <v>45058.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>122.95</v>
+        <v>122.2</v>
       </c>
       <c r="I16" t="n">
         <v>122.8634669392508</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.92</v>
+        <v>-3.51</v>
       </c>
       <c r="L16" t="n">
-        <v>3.51</v>
+        <v>3.87</v>
       </c>
       <c r="M16" t="n">
         <v>-0</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>125.6</v>
+        <v>127.15</v>
       </c>
       <c r="I17" t="n">
         <v>127.0246954070418</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.78</v>
+        <v>-4.05</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="M17" t="n">
         <v>0.97</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="O17" t="n">
         <v>-2.75</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.68</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45075.55208333334</v>
+        <v>45076.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>134.6</v>
+        <v>127.25</v>
       </c>
       <c r="I18" t="n">
         <v>129.5621548080015</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>5.86</v>
+        <v>0.08</v>
       </c>
       <c r="L18" t="n">
         <v>1.06</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08</v>
+        <v>6.32</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O18" t="n">
         <v>2.07</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.41</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45121.38541666666</v>
+        <v>45121.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>124.85</v>
+        <v>127.35</v>
       </c>
       <c r="I19" t="n">
         <v>126.0892207158915</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>1.89</v>
+        <v>-0.08</v>
       </c>
       <c r="L19" t="n">
         <v>1.02</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.53</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>123.7</v>
+        <v>120.7</v>
       </c>
       <c r="I20" t="n">
         <v>122.3134965970466</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.87</v>
+        <v>-5.22</v>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>5.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0.27</v>
+        <v>2.22</v>
       </c>
       <c r="N20" t="n">
-        <v>1.51</v>
+        <v>2.59</v>
       </c>
       <c r="O20" t="n">
         <v>2.95</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.11</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45173.38541666666</v>
+        <v>45173.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>105.05</v>
+        <v>106.4</v>
       </c>
       <c r="I21" t="n">
         <v>105.9174914536817</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>12.97</v>
+        <v>11.85</v>
       </c>
       <c r="L21" t="n">
         <v>3.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>4.48</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>102.6</v>
+        <v>100.9</v>
       </c>
       <c r="I22" t="n">
         <v>101.8106050644275</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.57</v>
+        <v>-5.17</v>
       </c>
       <c r="L22" t="n">
-        <v>3.99</v>
+        <v>5.59</v>
       </c>
       <c r="M22" t="n">
         <v>0.1</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.35</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>90.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>95.82809340650033</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>10.01</v>
+        <v>3.96</v>
       </c>
       <c r="L23" t="n">
         <v>4.56</v>
@@ -1752,7 +2027,7 @@
         <v>0.86</v>
       </c>
       <c r="N23" t="n">
-        <v>1.19</v>
+        <v>6.72</v>
       </c>
       <c r="O23" t="n">
         <v>-3.31</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.92</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>97</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>95.30878654356812</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1</v>
+        <v>-2.84</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
@@ -1809,7 +2096,7 @@
         <v>1.29</v>
       </c>
       <c r="N24" t="n">
-        <v>3.22</v>
+        <v>3.81</v>
       </c>
       <c r="O24" t="n">
         <v>6.72</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>97.3</v>
+        <v>99.3</v>
       </c>
       <c r="I25" t="n">
         <v>97.72748369486881</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.35</v>
+        <v>-5.47</v>
       </c>
       <c r="L25" t="n">
-        <v>5.1</v>
+        <v>5.47</v>
       </c>
       <c r="M25" t="n">
         <v>0.8</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45253.55208333334</v>
+        <v>45254.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>102.6</v>
+        <v>102</v>
       </c>
       <c r="I26" t="n">
         <v>102.2437710572828</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>3.32</v>
+        <v>2.72</v>
       </c>
       <c r="L26" t="n">
         <v>1.71</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45266.38541666666</v>
+        <v>45266.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>105.7</v>
+        <v>110.5</v>
       </c>
       <c r="I27" t="n">
         <v>106.5176962904634</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.63</v>
+        <v>-8.33</v>
       </c>
       <c r="L27" t="n">
-        <v>6.42</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.9</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.72</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>122.55</v>
+        <v>118.1</v>
       </c>
       <c r="I28" t="n">
         <v>119.0875770753977</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>10.9</v>
+        <v>6.88</v>
       </c>
       <c r="L28" t="n">
         <v>4.39</v>
@@ -2037,7 +2372,7 @@
         <v>1.66</v>
       </c>
       <c r="N28" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="O28" t="n">
         <v>3.85</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>123.85</v>
+        <v>125.3</v>
       </c>
       <c r="I29" t="n">
         <v>124.9162392686439</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.87</v>
+        <v>-6.1</v>
       </c>
       <c r="L29" t="n">
-        <v>5.55</v>
+        <v>6.44</v>
       </c>
       <c r="M29" t="n">
         <v>0.82</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>122.25</v>
+        <v>121.35</v>
       </c>
       <c r="I30" t="n">
         <v>121.5688502469887</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.43</v>
+        <v>-3.15</v>
       </c>
       <c r="L30" t="n">
         <v>3.79</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.01</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>127.95</v>
+        <v>130.9</v>
       </c>
       <c r="I31" t="n">
         <v>129.3716570478598</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.44</v>
+        <v>-7.87</v>
       </c>
       <c r="L31" t="n">
-        <v>6.63</v>
+        <v>7.99</v>
       </c>
       <c r="M31" t="n">
         <v>1.72</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>4.26</v>
       </c>
       <c r="O31" t="n">
         <v>-0.86</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>125.2</v>
+        <v>119.25</v>
       </c>
       <c r="I32" t="n">
         <v>123.1497044561455</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.35</v>
+        <v>-8.9</v>
       </c>
       <c r="L32" t="n">
-        <v>5.39</v>
+        <v>9.74</v>
       </c>
       <c r="M32" t="n">
-        <v>0.26</v>
+        <v>0.68</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>7.51</v>
       </c>
       <c r="O32" t="n">
         <v>4.26</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>126.25</v>
+        <v>132.3</v>
       </c>
       <c r="I33" t="n">
         <v>127.9028218753877</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.87</v>
+        <v>-10.94</v>
       </c>
       <c r="L33" t="n">
-        <v>6.92</v>
+        <v>11.53</v>
       </c>
       <c r="M33" t="n">
         <v>1.29</v>
       </c>
       <c r="N33" t="n">
-        <v>4.02</v>
+        <v>5.58</v>
       </c>
       <c r="O33" t="n">
         <v>-7.51</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.17</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>221.4</v>
+        <v>203.6</v>
       </c>
       <c r="I34" t="n">
         <v>213.1540798663837</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K34" t="n">
-        <v>67.34999999999999</v>
+        <v>53.89</v>
       </c>
       <c r="L34" t="n">
         <v>4.23</v>
@@ -2379,7 +2786,7 @@
         <v>1.67</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>8.24</v>
       </c>
       <c r="O34" t="n">
         <v>5.58</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.71</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45462.55208333334</v>
+        <v>45463.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>217</v>
+        <v>228.25</v>
       </c>
       <c r="I35" t="n">
         <v>227.4389265994562</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.58</v>
+        <v>-12.11</v>
       </c>
       <c r="L35" t="n">
-        <v>9.800000000000001</v>
+        <v>13.61</v>
       </c>
       <c r="M35" t="n">
         <v>2.49</v>
       </c>
       <c r="N35" t="n">
-        <v>4.58</v>
+        <v>4.79</v>
       </c>
       <c r="O35" t="n">
         <v>-8.24</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45469.55208333334</v>
+        <v>45470.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>213.45</v>
+        <v>210.85</v>
       </c>
       <c r="I36" t="n">
         <v>211.3858490406889</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.48</v>
+        <v>-7.62</v>
       </c>
       <c r="L36" t="n">
         <v>9.880000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.51</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>226.5</v>
+        <v>229.35</v>
       </c>
       <c r="I37" t="n">
         <v>228.6161010751335</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.42</v>
+        <v>-8.77</v>
       </c>
       <c r="L37" t="n">
-        <v>8.42</v>
+        <v>9.84</v>
       </c>
       <c r="M37" t="n">
         <v>0.96</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.51</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>217.5</v>
+        <v>214.35</v>
       </c>
       <c r="I38" t="n">
         <v>215.5249352745506</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.17</v>
+        <v>-6.54</v>
       </c>
       <c r="L38" t="n">
-        <v>7.02</v>
+        <v>7.22</v>
       </c>
       <c r="M38" t="n">
         <v>0.05</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.62</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>215.35</v>
+        <v>219.6</v>
       </c>
       <c r="I39" t="n">
         <v>216.3803373691545</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.47</v>
+        <v>-2.45</v>
       </c>
       <c r="L39" t="n">
         <v>4.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.31</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45546.38541666666</v>
+        <v>45546.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>218.65</v>
+        <v>215.2</v>
       </c>
       <c r="I40" t="n">
         <v>215.5911989680003</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.43</v>
+        <v>-2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="M40" t="n">
         <v>0.8</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>5.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45547.55208333334</v>
+        <v>45548.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>222.85</v>
+        <v>229.9</v>
       </c>
       <c r="I41" t="n">
         <v>227.7501515786901</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.55</v>
+        <v>-6.83</v>
       </c>
       <c r="L41" t="n">
-        <v>4.04</v>
+        <v>7.06</v>
       </c>
       <c r="M41" t="n">
         <v>0.88</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.71</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45581.38541666666</v>
+        <v>45581.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>247.45</v>
+        <v>245.55</v>
       </c>
       <c r="I42" t="n">
         <v>246.0281655451959</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>7.63</v>
+        <v>6.81</v>
       </c>
       <c r="L42" t="n">
         <v>4.05</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.78</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>232.65</v>
+        <v>234.45</v>
       </c>
       <c r="I43" t="n">
         <v>233.2458677288603</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="L43" t="n">
         <v>1.26</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>4.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>250.9</v>
+        <v>248.25</v>
       </c>
       <c r="I44" t="n">
         <v>248.9418672861589</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
-        <v>7.02</v>
+        <v>5.89</v>
       </c>
       <c r="L44" t="n">
         <v>0.75</v>
       </c>
       <c r="M44" t="n">
-        <v>0.28</v>
+        <v>2.97</v>
       </c>
       <c r="N44" t="n">
         <v>2.03</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>4.88</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>219.7</v>
+        <v>225.95</v>
       </c>
       <c r="I45" t="n">
         <v>223.8128095114968</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>11.5</v>
+        <v>8.98</v>
       </c>
       <c r="L45" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="N45" t="n">
         <v>4.58</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>223.5</v>
+        <v>218.05</v>
       </c>
       <c r="I46" t="n">
         <v>219.8226878260353</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.08</v>
+        <v>-3.5</v>
       </c>
       <c r="L46" t="n">
-        <v>2.15</v>
+        <v>4.67</v>
       </c>
       <c r="M46" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="N46" t="n">
-        <v>1.51</v>
+        <v>4.56</v>
       </c>
       <c r="O46" t="n">
         <v>3.5</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.56</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>223.9</v>
+        <v>229.85</v>
       </c>
       <c r="I47" t="n">
         <v>229.8258071129304</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.68</v>
+        <v>-5.41</v>
       </c>
       <c r="L47" t="n">
-        <v>4.24</v>
+        <v>5.64</v>
       </c>
       <c r="M47" t="n">
         <v>1.45</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>8.18</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>219.95</v>
+        <v>213.65</v>
       </c>
       <c r="I48" t="n">
         <v>214.7778339018487</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.31</v>
+        <v>-7.05</v>
       </c>
       <c r="L48" t="n">
-        <v>4.76</v>
+        <v>7.14</v>
       </c>
       <c r="M48" t="n">
-        <v>0.35</v>
+        <v>2.96</v>
       </c>
       <c r="N48" t="n">
         <v>4.35</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.76</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45721.38541666666</v>
+        <v>45721.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>213.8</v>
+        <v>215.95</v>
       </c>
       <c r="I49" t="n">
         <v>214.0418687609784</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.08</v>
       </c>
       <c r="L49" t="n">
         <v>4.49</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.84</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>230.8</v>
+        <v>222.1</v>
       </c>
       <c r="I50" t="n">
         <v>227.3818468960966</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>6.88</v>
+        <v>2.85</v>
       </c>
       <c r="L50" t="n">
         <v>1.04</v>
@@ -3291,7 +3890,7 @@
         <v>1.93</v>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>3.81</v>
       </c>
       <c r="O50" t="n">
         <v>4.86</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.02</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>201.65</v>
+        <v>207.55</v>
       </c>
       <c r="I51" t="n">
         <v>206.9440745462643</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>9.210000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="L51" t="n">
         <v>4.03</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45810.38541666666</v>
+        <v>45810.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>219</v>
+        <v>218.15</v>
       </c>
       <c r="I52" t="n">
         <v>218.4682798245126</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>5.52</v>
+        <v>5.11</v>
       </c>
       <c r="L52" t="n">
         <v>3.06</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.04</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>225.6</v>
+        <v>231.15</v>
       </c>
       <c r="I53" t="n">
         <v>229.1383516071373</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.42</v>
+        <v>-5.96</v>
       </c>
       <c r="L53" t="n">
-        <v>4.01</v>
+        <v>6.76</v>
       </c>
       <c r="M53" t="n">
-        <v>0.89</v>
+        <v>1.24</v>
       </c>
       <c r="N53" t="n">
-        <v>1.55</v>
+        <v>2.46</v>
       </c>
       <c r="O53" t="n">
         <v>-1</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.22</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>230.2</v>
+        <v>222.8</v>
       </c>
       <c r="I54" t="n">
         <v>225.8377421589005</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.41</v>
+        <v>-3.61</v>
       </c>
       <c r="L54" t="n">
-        <v>2.47</v>
+        <v>3.87</v>
       </c>
       <c r="M54" t="n">
         <v>1.79</v>
       </c>
       <c r="N54" t="n">
-        <v>2.18</v>
+        <v>3.54</v>
       </c>
       <c r="O54" t="n">
         <v>2.46</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>7.61</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>229.65</v>
+        <v>233.9</v>
       </c>
       <c r="I55" t="n">
         <v>233.4602718432939</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.07</v>
+        <v>-4.98</v>
       </c>
       <c r="L55" t="n">
-        <v>3.61</v>
+        <v>6.71</v>
       </c>
       <c r="M55" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="N55" t="n">
         <v>2.98</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.02</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>230</v>
+        <v>222.3</v>
       </c>
       <c r="I56" t="n">
         <v>224.2544498358231</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.67</v>
+        <v>-4.96</v>
       </c>
       <c r="L56" t="n">
-        <v>2.39</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M56" t="n">
         <v>0.42</v>
       </c>
       <c r="N56" t="n">
-        <v>2.53</v>
+        <v>3.15</v>
       </c>
       <c r="O56" t="n">
         <v>2.11</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.92</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>221.3</v>
+        <v>226.75</v>
       </c>
       <c r="I57" t="n">
         <v>224.3697973400606</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>0.45</v>
+        <v>-2</v>
       </c>
       <c r="L57" t="n">
         <v>4.79</v>
@@ -3690,7 +4373,7 @@
         <v>2.33</v>
       </c>
       <c r="N57" t="n">
-        <v>2.13</v>
+        <v>2.64</v>
       </c>
       <c r="O57" t="n">
         <v>-3.15</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.55</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>266.95</v>
+        <v>264.4</v>
       </c>
       <c r="I58" t="n">
         <v>264.7799327162615</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K58" t="n">
-        <v>17.73</v>
+        <v>16.6</v>
       </c>
       <c r="L58" t="n">
         <v>3.04</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.54</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45988.38541666666</v>
+        <v>45988.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>271.25</v>
+        <v>271.55</v>
       </c>
       <c r="I59" t="n">
         <v>271.4581097803949</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.59</v>
+        <v>-2.7</v>
       </c>
       <c r="L59" t="n">
         <v>3.69</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>274.25</v>
+        <v>270</v>
       </c>
       <c r="I60" t="n">
         <v>270.4256741625331</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K60" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="L60" t="n">
         <v>0.99</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.28</v>
       </c>
       <c r="M60" t="n">
         <v>0.41</v>
       </c>
       <c r="N60" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="O60" t="n">
         <v>0.5600000000000001</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.89</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46002.55208333334</v>
+        <v>46003.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>276.95</v>
+        <v>285.1</v>
       </c>
       <c r="I61" t="n">
         <v>281.0975443648467</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.57</v>
+        <v>-5.59</v>
       </c>
       <c r="L61" t="n">
-        <v>3.61</v>
+        <v>5.59</v>
       </c>
       <c r="M61" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="N61" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O61" t="n">
         <v>-2.46</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.06</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>401.9</v>
+        <v>364.45</v>
       </c>
       <c r="I62" t="n">
         <v>373.691790646137</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K62" t="n">
-        <v>40.97</v>
+        <v>27.83</v>
       </c>
       <c r="L62" t="n">
         <v>1.79</v>
       </c>
       <c r="M62" t="n">
-        <v>0.48</v>
+        <v>1.68</v>
       </c>
       <c r="N62" t="n">
-        <v>3.19</v>
+        <v>11.45</v>
       </c>
       <c r="O62" t="n">
         <v>2.6</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>13.58</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46077.55208333334</v>
+        <v>46078.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>365.3</v>
+        <v>378.6</v>
       </c>
       <c r="I63" t="n">
         <v>372.8965352830947</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.23</v>
+        <v>-3.88</v>
       </c>
       <c r="L63" t="n">
         <v>8.42</v>
@@ -4032,7 +4787,7 @@
         <v>5.13</v>
       </c>
       <c r="N63" t="n">
-        <v>2.71</v>
+        <v>4.38</v>
       </c>
       <c r="O63" t="n">
         <v>-11.45</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.02</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46093.55208333334</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>377.35</v>
+        <v>359.5</v>
       </c>
       <c r="I64" t="n">
         <v>363.4882004267651</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.33</v>
+        <v>-5.04</v>
       </c>
       <c r="L64" t="n">
-        <v>4.34</v>
+        <v>5.38</v>
       </c>
       <c r="M64" t="n">
         <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.87</v>
+        <v>4.58</v>
       </c>
       <c r="O64" t="n">
         <v>4.38</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>10.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>360.9</v>
+        <v>372.1</v>
       </c>
       <c r="I65" t="n">
         <v>364.2501599200448</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.39</v>
+        <v>-3.5</v>
       </c>
       <c r="L65" t="n">
-        <v>4.17</v>
+        <v>4.67</v>
       </c>
       <c r="M65" t="n">
         <v>2.96</v>
       </c>
       <c r="N65" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="O65" t="n">
         <v>-4.58</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.69</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>396.85</v>
+        <v>386.9</v>
       </c>
       <c r="I66" t="n">
         <v>389.8089156167676</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K66" t="n">
-        <v>6.65</v>
+        <v>3.98</v>
       </c>
       <c r="L66" t="n">
         <v>2.53</v>
@@ -4203,7 +4994,7 @@
         <v>1.32</v>
       </c>
       <c r="N66" t="n">
-        <v>1.98</v>
+        <v>2.89</v>
       </c>
       <c r="O66" t="n">
         <v>3.44</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46141.38541666666</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>397.05</v>
+        <v>405.65</v>
       </c>
       <c r="I67" t="n">
         <v>399.4480231330054</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.62</v>
+        <v>-4.85</v>
       </c>
       <c r="L67" t="n">
-        <v>3.14</v>
+        <v>5.52</v>
       </c>
       <c r="M67" t="n">
         <v>0.45</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.68</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>405.65</v>
+        <v>277.9</v>
       </c>
       <c r="I68" t="n">
         <v>374.4882921881725</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-31.49</v>
       </c>
       <c r="L68" t="n">
-        <v>2.13</v>
+        <v>33.07</v>
       </c>
       <c r="M68" t="n">
-        <v>-0</v>
+        <v>21.11</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>32.68</v>
       </c>
       <c r="O68" t="n">
         <v>4.39</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>30.02</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>323.9</v>
+        <v>334.8</v>
       </c>
       <c r="I69" t="n">
         <v>333.4326759769182</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K69" t="n">
-        <v>-16.55</v>
+        <v>-20.47</v>
       </c>
       <c r="L69" t="n">
-        <v>17.13</v>
+        <v>20.89</v>
       </c>
       <c r="M69" t="n">
         <v>1.96</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.02</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>333.6</v>
+        <v>328.25</v>
       </c>
       <c r="I70" t="n">
         <v>332.2203060709864</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.36</v>
+        <v>-1.96</v>
       </c>
       <c r="L70" t="n">
         <v>4.23</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>8.1</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46233.38541666666</v>
+        <v>46233.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>263.7</v>
+        <v>267</v>
       </c>
       <c r="I71" t="n">
         <v>265.5615847793858</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K71" t="n">
-        <v>19.66</v>
+        <v>18.66</v>
       </c>
       <c r="L71" t="n">
         <v>1.75</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>4.79</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>270.7</v>
+        <v>268</v>
       </c>
       <c r="I72" t="n">
         <v>270.3105094019105</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>1.39</v>
+        <v>0.37</v>
       </c>
       <c r="L72" t="n">
         <v>1.5</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>5.69</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>268.15</v>
+        <v>278.7</v>
       </c>
       <c r="I73" t="n">
         <v>273.6289227986575</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.06</v>
+        <v>-3.99</v>
       </c>
       <c r="L73" t="n">
-        <v>1.47</v>
+        <v>4.07</v>
       </c>
       <c r="M73" t="n">
         <v>1.22</v>
       </c>
       <c r="N73" t="n">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="O73" t="n">
         <v>-1.02</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>6.88</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>273.85</v>
+        <v>269.2</v>
       </c>
       <c r="I74" t="n">
         <v>270.8509917030444</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.74</v>
+        <v>-3.41</v>
       </c>
       <c r="L74" t="n">
-        <v>3.48</v>
+        <v>3.93</v>
       </c>
       <c r="M74" t="n">
         <v>1.11</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>6.52</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>268.7</v>
+        <v>270.25</v>
       </c>
       <c r="I75" t="n">
         <v>269.1512368462182</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K75" t="n">
-        <v>0.19</v>
+        <v>-0.39</v>
       </c>
       <c r="L75" t="n">
         <v>2.43</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>4.51</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>260.4</v>
+        <v>257.95</v>
       </c>
       <c r="I76" t="n">
         <v>258.0672901655092</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.64</v>
+        <v>-4.55</v>
       </c>
       <c r="L76" t="n">
-        <v>4.46</v>
+        <v>4.96</v>
       </c>
       <c r="M76" t="n">
         <v>0.87</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>4.67</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>254.3</v>
+        <v>264.25</v>
       </c>
       <c r="I77" t="n">
         <v>262.1028901061133</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>1.42</v>
+        <v>-2.44</v>
       </c>
       <c r="L77" t="n">
-        <v>0.99</v>
+        <v>2.89</v>
       </c>
       <c r="M77" t="n">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="N77" t="n">
-        <v>1.07</v>
+        <v>4.94</v>
       </c>
       <c r="O77" t="n">
         <v>-0.88</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,25 +5801,25 @@
         <v>6.7</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>256.35</v>
+        <v>250.6</v>
       </c>
       <c r="I78" t="n">
         <v>251.3731488013791</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.99</v>
+        <v>-5.17</v>
       </c>
       <c r="L78" t="n">
-        <v>4.03</v>
+        <v>5.37</v>
       </c>
       <c r="M78" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="N78" t="n">
         <v>2.66</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,12 @@
       <c r="Q79" t="n">
         <v>18</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.2</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.2</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="11">
@@ -7109,7 +8062,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -7119,7 +8072,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -7129,7 +8082,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -7139,7 +8092,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.98</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8102,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.85</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8112,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.05</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8122,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.34999999999999</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8132,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.6</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8142,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.16</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8152,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.01</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8162,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.13</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8172,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8182,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8192,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="25">
@@ -7249,7 +8202,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.63</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="26">
@@ -7259,7 +8212,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.39</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8222,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.59</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8232,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
